--- a/extension-libs/forms/contact/person-create.xlsx
+++ b/extension-libs/forms/contact/person-create.xlsx
@@ -528,10 +528,10 @@
     <t xml:space="preserve">name</t>
   </si>
   <si>
-    <t xml:space="preserve">label::English (en)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hint::English (en)</t>
+    <t xml:space="preserve">label::en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hint::en</t>
   </si>
   <si>
     <t xml:space="preserve">required</t>
@@ -827,16 +827,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1387,7 +1395,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1737,7 +1745,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="32.61"/>
   </cols>
   <sheetData>
@@ -1748,7 +1756,7 @@
       <c r="B1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1761,9 +1769,9 @@
       </c>
       <c r="B2" s="1" t="str">
         <f aca="true">TEXT(NOW(), "yyyymmddhhmmss")</f>
-        <v>20260722162907</v>
-      </c>
-      <c r="C2" s="2" t="s">
+        <v>20260722164248</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -1825,160 +1833,160 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="4" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="4" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="4" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="4" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="4" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="4" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="4" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="4" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="4" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="4" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="4" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="4" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="4" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="4" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="4" t="s">
         <v>72</v>
       </c>
     </row>
